--- a/plc/s7-1x00/core/adt/priority-queue/EPriorityQueueStatus-v1.0.xlsx
+++ b/plc/s7-1x00/core/adt/priority-queue/EPriorityQueueStatus-v1.0.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B5C680-4ACE-428B-AEBD-3FB7A9382E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Constants" state="visible" r:id="rId4"/>
+    <sheet name="Constants" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -37,9 +41,6 @@
     <t>Bool</t>
   </si>
   <si>
-    <t>{"version":"v1.0","author":"cyanezf","family":"core/adt/priority-queue"}</t>
-  </si>
-  <si>
     <t>PRIORITY_QUEUE_STATUS_0000_DONE</t>
   </si>
   <si>
@@ -146,19 +147,22 @@
   </si>
   <si>
     <t>Priority Queue: 0x8FFF - Error: Unknown method</t>
+  </si>
+  <si>
+    <t>{"version":"v1.0","author":"cyanezf","family":"core/adt/priority-queue","status": "current", "deprecatedBy": null, "dependencies"  : []}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -521,18 +525,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="42.142857142857146" customWidth="1"/>
-    <col min="3" max="3" width="9.714285714285714" customWidth="1"/>
-    <col min="4" max="4" width="9.285714285714286" customWidth="1"/>
-    <col min="5" max="5" width="73.28571428571429" customWidth="1"/>
-    <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="2" width="42.1796875" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" customWidth="1"/>
+    <col min="5" max="5" width="73.26953125" customWidth="1"/>
+    <col min="6" max="24" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -563,215 +567,215 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="E10" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="E12" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>